--- a/plantillas/74.xlsx
+++ b/plantillas/74.xlsx
@@ -12680,7 +12680,7 @@
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>PP SENIOR  ACTIVE MIND RZ MEDIANA 13KG · 93501261000</t>
+          <t>PP SENIOR  ACTIVE MIND RZ PQNA 3KG · 93510271000</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
@@ -12722,7 +12722,7 @@
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>PP SENIOR  ACTIVE MIND RZ PQNA 3KG · 93510271000</t>
+          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
@@ -12764,7 +12764,7 @@
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
+          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
+          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
+          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
+          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -14241,7 +14241,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -15961,7 +15961,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16621,7 +16621,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17921,7 +17921,7 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19061,7 +19061,7 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         </is>
       </c>
       <c r="C361" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         </is>
       </c>
       <c r="C362" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         </is>
       </c>
       <c r="C366" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -20721,7 +20721,7 @@
         </is>
       </c>
       <c r="C367" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         </is>
       </c>
       <c r="C410" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -22681,7 +22681,7 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         </is>
       </c>
       <c r="C522" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         </is>
       </c>
       <c r="C546" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -24541,7 +24541,7 @@
         </is>
       </c>
       <c r="C558" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         </is>
       </c>
       <c r="C591" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         </is>
       </c>
       <c r="C602" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -25532,16 +25532,16 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>PP SENIOR  ACTIVE MIND RZ MEDIANA 13KG · 93501261000</t>
+          <t>PP SENIOR  ACTIVE MIND RZ PQNA 3KG · 93510271000</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>93501261000</t>
+          <t>93510271000</t>
         </is>
       </c>
       <c r="C608" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -25552,16 +25552,16 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>PP SENIOR  ACTIVE MIND RZ PQNA 3KG · 93510271000</t>
+          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>93510271000</t>
+          <t>93519400000</t>
         </is>
       </c>
       <c r="C609" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -25572,16 +25572,16 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>PP VET GATOS FORTI-FLORA 30X1.06OZ · 93519400000</t>
+          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>93519400000</t>
+          <t>90038410000</t>
         </is>
       </c>
       <c r="C610" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -25592,12 +25592,12 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>PPVD GATO SOBREPESO 6LB · 90038410000</t>
+          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>90038410000</t>
+          <t>90038380000</t>
         </is>
       </c>
       <c r="C611" t="n">
@@ -25612,16 +25612,16 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>PPVD NC NEUROCARE 6LB · 90038380000</t>
+          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>90038380000</t>
+          <t>90038430000</t>
         </is>
       </c>
       <c r="C612" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -25632,16 +25632,16 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>PPVD NUTRICION CRITICA GATO Y PERRO 5.5O · 90038430000</t>
+          <t>PPVD PERRO URINARY 6LB · 90038390000</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>90038430000</t>
+          <t>90038390000</t>
         </is>
       </c>
       <c r="C613" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         </is>
       </c>
       <c r="C615" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -25801,7 +25801,7 @@
         </is>
       </c>
       <c r="C621" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -26061,7 +26061,7 @@
         </is>
       </c>
       <c r="C634" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -27061,7 +27061,7 @@
         </is>
       </c>
       <c r="C684" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         </is>
       </c>
       <c r="C690" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         </is>
       </c>
       <c r="C731" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         </is>
       </c>
       <c r="C746" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         </is>
       </c>
       <c r="C747" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         </is>
       </c>
       <c r="C753" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         </is>
       </c>
       <c r="C754" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         </is>
       </c>
       <c r="C762" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -28721,7 +28721,7 @@
         </is>
       </c>
       <c r="C767" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         </is>
       </c>
       <c r="C791" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         </is>
       </c>
       <c r="C794" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -29559,7 +29559,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>19.10.2026</t>
+          <t>20.10.2026</t>
         </is>
       </c>
     </row>
